--- a/ci-cd-merge-resolver/repoCollector/datasets/bt.xlsx
+++ b/ci-cd-merge-resolver/repoCollector/datasets/bt.xlsx
@@ -62,6 +62,15 @@
     <t>0e20cacbe9c69a7aee829d3cd36278b693e89246</t>
   </si>
   <si>
+    <t>1c5db27b90c9ffabef0766f5142f0baca5741439</t>
+  </si>
+  <si>
+    <t>dc756988c553a4a1f8ebc9ba1cbd7608877f8235</t>
+  </si>
+  <si>
+    <t>16c438449c4c5728d5543c394946ed729977e108</t>
+  </si>
+  <si>
     <t>2525fb8ad22e111dd81e07c9a64890cc51799825</t>
   </si>
   <si>
@@ -69,15 +78,6 @@
   </si>
   <si>
     <t>525acac3d4451273cdb6911067c5c8bf89e00960</t>
-  </si>
-  <si>
-    <t>1c5db27b90c9ffabef0766f5142f0baca5741439</t>
-  </si>
-  <si>
-    <t>dc756988c553a4a1f8ebc9ba1cbd7608877f8235</t>
-  </si>
-  <si>
-    <t>16c438449c4c5728d5543c394946ed729977e108</t>
   </si>
   <si>
     <t>b9820ecd024eba54a47cb20d03e20b23a5e27e74</t>
@@ -195,7 +195,7 @@
         <v>12</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>84.0</v>
+        <v>161.0</v>
       </c>
       <c r="E2" t="n" s="0">
         <v>1.0</v>
@@ -210,10 +210,10 @@
         <v>1</v>
       </c>
       <c r="I2" t="n" s="0">
-        <v>1.0890001058578491</v>
+        <v>1.4710001945495605</v>
       </c>
       <c r="J2" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -227,7 +227,7 @@
         <v>15</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>49.0</v>
+        <v>51.0</v>
       </c>
       <c r="E3" t="n" s="0">
         <v>1.0</v>
@@ -242,10 +242,10 @@
         <v>1</v>
       </c>
       <c r="I3" t="n" s="0">
-        <v>1.4479999542236328</v>
+        <v>2.0169999599456787</v>
       </c>
       <c r="J3" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -259,7 +259,7 @@
         <v>18</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>102.0</v>
+        <v>246.0</v>
       </c>
       <c r="E4" t="n" s="0">
         <v>1.0</v>
@@ -274,10 +274,10 @@
         <v>1</v>
       </c>
       <c r="I4" t="n" s="0">
-        <v>1.2209999561309814</v>
+        <v>2.292999744415283</v>
       </c>
       <c r="J4" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -291,7 +291,7 @@
         <v>21</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>143.0</v>
+        <v>179.0</v>
       </c>
       <c r="E5" t="n" s="0">
         <v>1.0</v>
@@ -306,10 +306,10 @@
         <v>1</v>
       </c>
       <c r="I5" t="n" s="0">
-        <v>1.7740004062652588</v>
+        <v>1.9009997844696045</v>
       </c>
       <c r="J5" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -323,7 +323,7 @@
         <v>24</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>192.0</v>
+        <v>303.0</v>
       </c>
       <c r="E6" t="n" s="0">
         <v>1.0</v>
@@ -338,10 +338,10 @@
         <v>1</v>
       </c>
       <c r="I6" t="n" s="0">
-        <v>0.8100000619888306</v>
+        <v>1.2989997863769531</v>
       </c>
       <c r="J6" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -355,7 +355,7 @@
         <v>27</v>
       </c>
       <c r="D7" t="n" s="0">
-        <v>220.0</v>
+        <v>335.0</v>
       </c>
       <c r="E7" t="n" s="0">
         <v>1.0</v>
@@ -370,10 +370,10 @@
         <v>1</v>
       </c>
       <c r="I7" t="n" s="0">
-        <v>2.559999704360962</v>
+        <v>2.5380003452301025</v>
       </c>
       <c r="J7" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -387,7 +387,7 @@
         <v>30</v>
       </c>
       <c r="D8" t="n" s="0">
-        <v>265.0</v>
+        <v>334.0</v>
       </c>
       <c r="E8" t="n" s="0">
         <v>1.0</v>
@@ -402,10 +402,10 @@
         <v>1</v>
       </c>
       <c r="I8" t="n" s="0">
-        <v>4.573999881744385</v>
+        <v>4.100000381469727</v>
       </c>
       <c r="J8" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
